--- a/static/files/test.xlsx
+++ b/static/files/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2312AAC4-B660-407E-9355-D397A33049FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0FA929-7324-4CE5-9810-E71D79AC9A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
   <si>
     <t>Target</t>
   </si>
@@ -42,13 +42,19 @@
     <t>Dmax Score</t>
   </si>
   <si>
-    <t>Approval Status</t>
-  </si>
-  <si>
     <t>SNO</t>
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>New initiatives</t>
   </si>
 </sst>
 </file>
@@ -90,16 +96,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,38 +389,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="21.109375" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="9" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="1"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>0</v>
       </c>
@@ -424,10 +449,17 @@
       <c r="F2" t="s">
         <v>1</v>
       </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/static/files/test.xlsx
+++ b/static/files/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0FA929-7324-4CE5-9810-E71D79AC9A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D678722-C04C-43CF-9736-78971C39E306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t>Target</t>
   </si>
@@ -55,6 +55,18 @@
   </si>
   <si>
     <t>New initiatives</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>New Initiatives</t>
+  </si>
+  <si>
+    <t>Emp Id</t>
   </si>
 </sst>
 </file>
@@ -84,7 +96,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -92,21 +104,68 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -389,78 +448,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="21.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="16" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="3" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="4"/>
+      <c r="J1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="5"/>
+      <c r="L1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="5"/>
+      <c r="N1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="7"/>
+      <c r="P1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
+  <mergeCells count="5">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
